--- a/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,22 +82,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARIAM MICHAELL</t>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>JOSUE YAHIR</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
   </si>
   <si>
     <t>DENISSE</t>
+  </si>
+  <si>
+    <t>IAN</t>
   </si>
 </sst>
 </file>
@@ -693,16 +744,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -716,16 +770,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -739,16 +796,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -762,16 +822,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>88.56999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -785,16 +848,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>70.83</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -808,16 +874,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>97.3</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -882,7 +951,7 @@
         <v>79.17</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -899,16 +968,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,7 +1003,7 @@
         <v>92.86</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,7 +1029,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,7 +1055,7 @@
         <v>70.83</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1003,16 +1072,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>91.89</v>
+        <v>97.3</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,22 +1123,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920088</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1077,24 +1146,185 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920065</v>
+        <v>23330051920023</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920251</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920097</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920112</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920357</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920065</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920043</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -106,9 +106,15 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
@@ -121,9 +127,15 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>RAFAEL FELIPE</t>
   </si>
   <si>
@@ -148,7 +160,13 @@
     <t>DENISSE</t>
   </si>
   <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
     <t>IAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,7 +1150,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1152,10 +1170,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,10 +1193,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1198,10 +1216,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1221,10 +1239,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1247,7 +1265,7 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1267,10 +1285,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1290,10 +1308,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1307,16 +1325,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920043</v>
+        <v>23330051920181</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1325,6 +1343,52 @@
         <v>13</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920043</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920212</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -115,6 +136,24 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
@@ -134,6 +173,27 @@
   </si>
   <si>
     <t>VILLA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JULIO EDUARDO</t>
   </si>
   <si>
     <t>RAFAEL FELIPE</t>
@@ -1109,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1141,22 +1201,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920006</v>
+        <v>23330051920081</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1164,22 +1224,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920023</v>
+        <v>23330051920072</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1187,22 +1247,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920025</v>
+        <v>23330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1210,22 +1270,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920251</v>
+        <v>23330051920037</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1233,22 +1293,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920097</v>
+        <v>22330051920021</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1256,22 +1316,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920112</v>
+        <v>23330051920045</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1279,7 +1339,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920357</v>
+        <v>22330051920424</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1288,13 +1348,13 @@
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1302,94 +1362,255 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920065</v>
+        <v>23330051920006</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920181</v>
+        <v>23330051920023</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920043</v>
+        <v>23330051920025</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920212</v>
+        <v>23330051920251</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920097</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920357</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920065</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920181</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920043</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920212</v>
+      </c>
+      <c r="B19" t="s">
         <v>38</v>
       </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G12">
-        <v>2</v>
+      <c r="G19">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,18 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -130,12 +142,15 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
@@ -173,6 +188,18 @@
   </si>
   <si>
     <t>VILLA</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -1169,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1201,30 +1228,30 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920081</v>
+        <v>23330051920022</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1233,7 +1260,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1242,73 +1269,73 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920028</v>
+        <v>23330051920017</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920037</v>
+        <v>23330051920313</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920021</v>
+        <v>23330051920081</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1316,22 +1343,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920045</v>
+        <v>23330051920072</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1339,22 +1366,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920424</v>
+        <v>23330051920028</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1362,114 +1389,114 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920006</v>
+        <v>23330051920037</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920023</v>
+        <v>22330051920021</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920025</v>
+        <v>23330051920045</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920251</v>
+        <v>22330051920424</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920097</v>
+        <v>23330051920006</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1477,22 +1504,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920112</v>
+        <v>23330051920023</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1500,22 +1527,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920357</v>
+        <v>23330051920025</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1523,22 +1550,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920065</v>
+        <v>23330051920251</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1546,22 +1573,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920181</v>
+        <v>23330051920097</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1569,22 +1596,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920043</v>
+        <v>23330051920112</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1592,24 +1619,116 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920212</v>
+        <v>23330051920357</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920065</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920181</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
         <v>13</v>
       </c>
-      <c r="G19">
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920043</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920212</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
@@ -82,175 +82,175 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>TELLO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
+    <t>MARIN</t>
   </si>
   <si>
     <t>VIVANCO</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
+  </si>
+  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>ANGEL YAMIL</t>
+    <t>ABRIL</t>
   </si>
   <si>
     <t>LUIS AARON</t>
   </si>
   <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>JULIO EDUARDO</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>JOSUE YAHIR</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>IAN</t>
   </si>
   <si>
     <t>URIEL</t>
-  </si>
-  <si>
-    <t>JULIO EDUARDO</t>
-  </si>
-  <si>
-    <t>RAFAEL FELIPE</t>
-  </si>
-  <si>
-    <t>JOSUE YAHIR</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>IAN</t>
   </si>
   <si>
     <t>ALEX URIEL</t>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1246,7 +1246,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1257,7 +1257,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>58</v>
@@ -1269,12 +1269,12 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920017</v>
+        <v>23330051920022</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1292,18 +1292,18 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920313</v>
+        <v>23330051920097</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
         <v>60</v>
@@ -1312,21 +1312,21 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920081</v>
+        <v>23330051920313</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
         <v>61</v>
@@ -1335,7 +1335,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1349,7 +1349,7 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>62</v>
@@ -1372,7 +1372,7 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -1395,7 +1395,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
@@ -1418,7 +1418,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>65</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920045</v>
+        <v>22330051920424</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
         <v>66</v>
@@ -1450,7 +1450,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1458,13 +1458,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920424</v>
+        <v>23330051920006</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
         <v>67</v>
@@ -1473,21 +1473,21 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920006</v>
+        <v>23330051920023</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>68</v>
@@ -1504,13 +1504,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920023</v>
+        <v>23330051920025</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
         <v>69</v>
@@ -1527,13 +1527,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920025</v>
+        <v>23330051920081</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>70</v>
@@ -1542,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1556,7 +1556,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>71</v>
@@ -1573,13 +1573,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920097</v>
+        <v>23330051920112</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -1596,13 +1596,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920112</v>
+        <v>23330051920357</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>73</v>
@@ -1611,7 +1611,7 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920357</v>
+        <v>23330051920065</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920065</v>
+        <v>23330051920181</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920181</v>
+        <v>23330051920043</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>54</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920043</v>
+        <v>23330051920045</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
         <v>55</v>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,178 +82,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MONTERD</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TELLO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>COLMENARES</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>UTRERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
+    <t>JUAN YAHEL</t>
   </si>
   <si>
     <t>ANGEL YAMIL</t>
   </si>
   <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
+    <t>CARLOS DAVID</t>
   </si>
   <si>
     <t>JULIO EDUARDO</t>
   </si>
   <si>
-    <t>RAFAEL FELIPE</t>
-  </si>
-  <si>
     <t>JOSUE YAHIR</t>
   </si>
   <si>
     <t>JUAN ALBERTO</t>
   </si>
   <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>JESUS JAREF</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>ALEX URIEL</t>
+    <t>ARIADNA JARETZI</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +945,7 @@
         <v>79.17</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1073,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>97.22</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1099,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1125,16 +1014,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1151,16 +1040,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>70.83</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1186,7 +1075,7 @@
         <v>97.3</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,16 +1117,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1251,22 +1140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920071</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1274,16 +1163,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920022</v>
+        <v>23330051920018</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1297,22 +1186,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920097</v>
+        <v>22330051920424</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1320,415 +1209,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920313</v>
+        <v>23330051920023</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920072</v>
+        <v>23330051920025</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920028</v>
+        <v>23330051920111</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920037</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920021</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920424</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920006</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920023</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920025</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920081</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920251</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920112</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920357</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920065</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920181</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920043</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920045</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920212</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
         <v>1</v>
       </c>
     </row>
